--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3387" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -662,6 +662,15 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis"/&gt;
+    &lt;code value="MED-145"/&gt;
+    &lt;display value="Transfusion de produits sanguins"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -689,7 +698,187 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>Observation.code.id</t>
+    <t>Observation.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
+</t>
+  </si>
+  <si>
+    <t>Patient concerné</t>
+  </si>
+  <si>
+    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+  </si>
+  <si>
+    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
+  </si>
+  <si>
+    <t>Observations have no value if you don't know who or what they're about.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>participation[typeCode=RTGT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>What the observation is about, when it is not about the subject of record</t>
+  </si>
+  <si>
+    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
+  </si>
+  <si>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>Observation.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-encounter-document)
+</t>
+  </si>
+  <si>
+    <t>Rencontre de soins durant laquelle cette observation a été effectuée</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
+  </si>
+  <si>
+    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occurrence
+</t>
+  </si>
+  <si>
+    <t>dateTime
+PeriodTiminginstant</t>
+  </si>
+  <si>
+    <t>Date de l'observation</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+  </si>
+  <si>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+  </si>
+  <si>
+    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>Date/Time this version was made available</t>
+  </si>
+  <si>
+    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
+  </si>
+  <si>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Observation.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who is responsible for the observation</t>
+  </si>
+  <si>
+    <t>Who was responsible for asserting the observed value as "true".</t>
+  </si>
+  <si>
+    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:extension.url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -708,7 +897,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.code.extension</t>
+    <t>Observation.performer.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -721,375 +910,7 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>MED-145</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Transfusion de produits sanguins</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
-</t>
-  </si>
-  <si>
-    <t>Patient concerné</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
-  </si>
-  <si>
-    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
-  </si>
-  <si>
-    <t>Observations have no value if you don't know who or what they're about.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>participation[typeCode=RTGT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Observation.focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>What the observation is about, when it is not about the subject of record</t>
-  </si>
-  <si>
-    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
-  </si>
-  <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>Observation.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-encounter-document)
-</t>
-  </si>
-  <si>
-    <t>Rencontre de soins durant laquelle cette observation a été effectuée</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
-  </si>
-  <si>
-    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence
-</t>
-  </si>
-  <si>
-    <t>dateTime
-PeriodTiminginstant</t>
-  </si>
-  <si>
-    <t>Date de l'observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
-  </si>
-  <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.issued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
-  </si>
-  <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:extension.url}
-</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.performer.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension</t>
   </si>
   <si>
     <t>Observation.performer.extension:author</t>
@@ -1329,6 +1150,10 @@
   </si>
   <si>
     <t>Observation.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
   </si>
   <si>
     <t>Valeur de l'observation</t>
@@ -2181,7 +2006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP88"/>
+  <dimension ref="A1:AP77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.22265625" customWidth="true" bestFit="true"/>
@@ -4089,7 +3914,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -4104,13 +3929,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4143,30 +3968,30 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4174,31 +3999,35 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -4246,7 +4075,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4258,22 +4087,22 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4281,14 +4110,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4304,19 +4133,19 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>140</v>
+        <v>229</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4354,16 +4183,16 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>227</v>
@@ -4378,7 +4207,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4387,13 +4216,13 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4401,21 +4230,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4427,19 +4256,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4488,13 +4317,13 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
@@ -4503,62 +4332,66 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4606,7 +4439,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4618,22 +4451,22 @@
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4641,21 +4474,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4664,19 +4497,19 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>139</v>
+        <v>256</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>140</v>
+        <v>257</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>142</v>
+        <v>259</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4714,31 +4547,31 @@
         <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -4747,13 +4580,13 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4761,10 +4594,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4775,10 +4608,10 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>82</v>
@@ -4787,19 +4620,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
+        <v>264</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4809,7 +4640,7 @@
         <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>82</v>
@@ -4836,25 +4667,23 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4863,19 +4692,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4883,10 +4712,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4906,20 +4735,18 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4968,7 +4795,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4980,7 +4807,7 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4989,10 +4816,10 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5003,21 +4830,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -5026,21 +4853,21 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>140</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5049,7 +4876,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5076,31 +4903,31 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5109,10 +4936,10 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5123,12 +4950,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5137,7 +4966,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5146,21 +4975,19 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>217</v>
+        <v>287</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>266</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5169,7 +4996,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -5208,19 +5035,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5229,10 +5056,10 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5243,10 +5070,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5266,23 +5093,19 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5330,7 +5153,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5342,7 +5165,7 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5351,7 +5174,7 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>279</v>
@@ -5365,10 +5188,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5376,10 +5199,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5388,23 +5211,19 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5440,31 +5259,31 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5473,10 +5292,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5485,14 +5304,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5504,29 +5325,25 @@
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>289</v>
+        <v>139</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5574,34 +5391,34 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5609,10 +5426,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5623,7 +5440,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5632,20 +5449,18 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5694,19 +5509,19 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5715,13 +5530,13 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5729,21 +5544,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5752,23 +5567,19 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>139</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5804,61 +5615,61 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5868,35 +5679,33 @@
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>317</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>82</v>
@@ -5938,10 +5747,10 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>93</v>
@@ -5950,22 +5759,22 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>324</v>
+        <v>136</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5973,10 +5782,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5996,20 +5805,18 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>327</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6019,7 +5826,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -6034,13 +5841,11 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -6058,7 +5863,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6079,13 +5884,13 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>332</v>
+        <v>136</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -6093,12 +5898,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6107,30 +5914,28 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>335</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>337</v>
+        <v>296</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6166,17 +5971,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6188,22 +5995,22 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6211,10 +6018,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6237,13 +6044,13 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>219</v>
+        <v>277</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6294,7 +6101,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6318,7 +6125,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6329,21 +6136,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6358,14 +6165,12 @@
         <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6402,19 +6207,19 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>225</v>
+        <v>283</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6438,7 +6243,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6449,23 +6254,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6477,22 +6280,24 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>348</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6534,19 +6339,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>227</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6558,7 +6363,7 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6569,10 +6374,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6595,13 +6400,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>218</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>219</v>
+        <v>312</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6652,7 +6457,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>220</v>
+        <v>315</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6664,7 +6469,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6676,7 +6481,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6687,21 +6492,23 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>355</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6716,10 +6523,10 @@
         <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>295</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>296</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6758,19 +6565,19 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6805,20 +6612,18 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
@@ -6833,13 +6638,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>139</v>
+        <v>275</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6890,19 +6695,19 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6914,7 +6719,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6925,10 +6730,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6939,7 +6744,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6951,13 +6756,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>218</v>
+        <v>295</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>219</v>
+        <v>296</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6996,31 +6801,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7032,7 +6837,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7043,10 +6848,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7054,10 +6859,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7069,22 +6874,24 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>356</v>
+        <v>305</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>82</v>
@@ -7114,31 +6921,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>227</v>
+        <v>308</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7150,7 +6957,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7161,10 +6968,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7172,7 +6979,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
@@ -7187,24 +6994,22 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>366</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>82</v>
@@ -7246,10 +7051,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>93</v>
@@ -7258,7 +7063,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7281,10 +7086,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7292,7 +7097,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7307,25 +7112,27 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7340,11 +7147,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7362,10 +7171,10 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>376</v>
+        <v>308</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
@@ -7374,7 +7183,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7397,14 +7206,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7413,7 +7220,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7425,13 +7232,13 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>139</v>
+        <v>335</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>357</v>
+        <v>312</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7482,19 +7289,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7506,7 +7313,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7517,10 +7324,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7540,18 +7347,20 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7600,7 +7409,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7609,10 +7418,10 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7624,7 +7433,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7635,10 +7444,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7649,7 +7458,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7658,18 +7467,20 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7694,43 +7505,43 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>227</v>
+        <v>349</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7742,7 +7553,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7753,10 +7564,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7764,7 +7575,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -7776,19 +7587,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7796,7 +7607,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -7838,10 +7649,10 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>93</v>
@@ -7850,7 +7661,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7862,7 +7673,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>136</v>
+        <v>355</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7873,10 +7684,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7896,18 +7707,20 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>275</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7956,7 +7769,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7989,16 +7802,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8010,25 +7821,29 @@
         <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>139</v>
+        <v>362</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8076,45 +7891,45 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>227</v>
+        <v>361</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8137,16 +7952,20 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>218</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8170,13 +7989,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8194,7 +8013,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>220</v>
+        <v>372</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8203,10 +8022,10 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8215,10 +8034,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>221</v>
+        <v>380</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8227,26 +8046,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -8255,16 +8074,20 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8288,31 +8111,29 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>227</v>
+        <v>381</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8324,33 +8145,33 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8358,13 +8179,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8373,24 +8194,26 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>393</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8432,19 +8255,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8453,10 +8276,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>136</v>
+        <v>399</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8465,12 +8288,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8484,7 +8307,7 @@
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8493,15 +8316,17 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>390</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8526,13 +8351,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8550,7 +8375,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8568,27 +8393,27 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>136</v>
+        <v>408</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8596,13 +8421,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8611,24 +8436,26 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>366</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>367</v>
+        <v>412</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -8646,13 +8473,11 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8670,10 +8495,10 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>93</v>
@@ -8682,7 +8507,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8691,10 +8516,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>136</v>
+        <v>417</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8705,10 +8530,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8719,7 +8544,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8731,15 +8556,17 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8788,7 +8615,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>376</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8806,27 +8633,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>136</v>
+        <v>425</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8846,19 +8673,19 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>217</v>
+        <v>428</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>429</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8908,7 +8735,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8917,7 +8744,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -8926,27 +8753,27 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>136</v>
+        <v>434</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8957,7 +8784,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8966,21 +8793,23 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>437</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9004,13 +8833,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9028,19 +8857,19 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>442</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9049,10 +8878,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>136</v>
+        <v>444</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9063,10 +8892,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9086,20 +8915,18 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>412</v>
+        <v>276</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9148,7 +8975,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>278</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9160,7 +8987,7 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9172,7 +8999,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>416</v>
+        <v>279</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9183,21 +9010,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9206,19 +9033,19 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>418</v>
+        <v>140</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>419</v>
+        <v>281</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>420</v>
+        <v>142</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9268,19 +9095,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>284</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9292,7 +9119,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>136</v>
+        <v>279</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9301,47 +9128,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>272</v>
+        <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>425</v>
+        <v>142</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>426</v>
+        <v>148</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9390,45 +9217,45 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>430</v>
+        <v>136</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9451,20 +9278,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>192</v>
+        <v>453</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9488,13 +9311,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9512,7 +9335,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9521,7 +9344,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9533,10 +9356,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>136</v>
+        <v>457</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9545,16 +9368,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9564,7 +9387,7 @@
         <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
@@ -9573,20 +9396,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>453</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9610,11 +9429,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9632,16 +9453,16 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9650,27 +9471,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9681,10 +9502,10 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
@@ -9693,19 +9514,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>453</v>
+        <v>192</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9730,13 +9551,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9754,13 +9575,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9772,13 +9593,13 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>459</v>
+        <v>390</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9787,12 +9608,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9803,10 +9624,10 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
@@ -9818,15 +9639,17 @@
         <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9850,13 +9673,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9874,13 +9697,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9892,27 +9715,27 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>468</v>
+        <v>390</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9926,7 +9749,7 @@
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
@@ -9935,19 +9758,17 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>192</v>
+        <v>480</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9972,11 +9793,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -9994,7 +9817,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10015,10 +9838,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10029,10 +9852,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10055,17 +9878,15 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>479</v>
+        <v>275</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10114,7 +9935,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10132,27 +9953,27 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10163,7 +9984,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10172,19 +9993,19 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10234,13 +10055,13 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
@@ -10252,19 +10073,19 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -10292,7 +10113,7 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>497</v>
@@ -10306,9 +10127,7 @@
       <c r="N68" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="O68" t="s" s="2">
-        <v>501</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10368,7 +10187,7 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>502</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10377,10 +10196,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10391,10 +10210,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10405,7 +10224,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10414,19 +10233,23 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>217</v>
+        <v>437</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>218</v>
+        <v>503</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10474,19 +10297,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>220</v>
+        <v>502</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10495,10 +10318,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>221</v>
+        <v>508</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10509,21 +10332,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10535,17 +10358,15 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>139</v>
+        <v>275</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>140</v>
+        <v>276</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10594,19 +10415,19 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10618,7 +10439,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10629,14 +10450,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>508</v>
+        <v>138</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10649,26 +10470,24 @@
         <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>509</v>
+        <v>140</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>510</v>
+        <v>281</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O71" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10716,7 +10535,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>511</v>
+        <v>284</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10740,7 +10559,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>136</v>
+        <v>279</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10751,42 +10570,46 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>513</v>
+        <v>139</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>449</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -10834,19 +10657,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>512</v>
+        <v>451</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10855,10 +10678,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>518</v>
+        <v>136</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10869,10 +10692,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10880,7 +10703,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>93</v>
@@ -10892,19 +10715,23 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L73" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="M73" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -10928,13 +10755,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -10952,16 +10779,16 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -10970,16 +10797,16 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>517</v>
+        <v>213</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>522</v>
+        <v>214</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>82</v>
@@ -10987,10 +10814,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11010,22 +10837,22 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>192</v>
+        <v>518</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>525</v>
+        <v>364</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>527</v>
+        <v>366</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11050,13 +10877,13 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11074,7 +10901,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11092,27 +10919,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>531</v>
+        <v>369</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11123,7 +10950,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11138,16 +10965,16 @@
         <v>192</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>536</v>
+        <v>376</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11172,13 +10999,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>207</v>
+        <v>346</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>537</v>
+        <v>377</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>538</v>
+        <v>378</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11196,16 +11023,16 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11214,13 +11041,13 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>531</v>
+        <v>136</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11231,21 +11058,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11257,17 +11084,19 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>540</v>
+        <v>192</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>543</v>
+        <v>386</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11292,13 +11121,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11316,13 +11145,13 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
@@ -11334,27 +11163,27 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>544</v>
+        <v>390</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11365,7 +11194,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11377,16 +11206,20 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11434,13 +11267,13 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
@@ -11455,1352 +11288,20 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>517</v>
+        <v>443</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>548</v>
+        <v>444</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP88" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP88">
+  <autoFilter ref="A1:AP77">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12810,7 +11311,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI87">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-blood-product-transfusion-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
